--- a/TwilioSender.xlsx
+++ b/TwilioSender.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/ashish_d_jain_oracle_com/Documents/Git/Twilio_Sender/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://oracle-my.sharepoint.com/personal/ashish_d_jain_oracle_com/Documents/Git/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="62" documentId="11_1CC3CF581A929D46026E3B5F72E494CCFDFA7F19" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A0EE69A-D092-40CB-8BD3-B334FDB7839D}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="490" windowWidth="19420" windowHeight="10900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -334,6 +334,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -343,9 +346,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,28 +659,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
     </row>
     <row r="4" spans="1:4" ht="100" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" s="2" t="s">
@@ -694,20 +694,20 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
     </row>
     <row r="8" spans="1:4" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1033,7 +1033,7 @@
       <c r="A4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>52</v>
       </c>
     </row>

--- a/TwilioSender.xlsx
+++ b/TwilioSender.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Contacts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Templates" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -518,12 +519,23 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Messages Per Second (MPS):</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>&lt;- Set your desired sending rate (e.g., 1).</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Button Placeholder</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="n"/>
     </row>
     <row r="8" ht="50" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
@@ -550,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:S4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -561,6 +573,17 @@
     <col width="15" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -604,6 +627,61 @@
           <t>Variable {{4}}</t>
         </is>
       </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{5}}</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{6}}</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{7}}</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{8}}</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{9}}</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{10}}</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{11}}</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{12}}</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{13}}</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{14}}</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>Variable {{15}}</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -637,11 +715,18 @@
           <t>Value3A</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Value4A</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -670,16 +755,19 @@
           <t>Value2B</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Value3B</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Value4B</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -718,6 +806,17 @@
           <t>Value4C</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -871,4 +970,58 @@
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DC11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Contact Number</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Message UID</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Twilio Response</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/TwilioSender.xlsx
+++ b/TwilioSender.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Contacts" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Templates" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Settings" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Log" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Log" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Settings" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,10 +43,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00595959"/>
     </font>
   </fonts>
   <fills count="4">
@@ -81,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -91,18 +87,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,12 +453,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
@@ -494,11 +479,11 @@
     <row r="4" ht="100" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>1. Go to the 'Settings' sheet and enter your Twilio Account SID, Auth Token, and 'From' number.
-2. Go to the 'Contacts' sheet and add your contacts' names and numbers. Set 'Send?' to 'Yes' for those you want to message.
-3. Go to the 'Templates' sheet to define your messages. Make sure each message has a unique 'Message UID'.
-4. Come back to this Dashboard and enter the Message UID for your chosen message into the yellow box at C5.
-5. Click the 'Send Messages' button (which will be added after embedding the macro) to send the messages.</t>
+          <t>1. Go to 'Settings' to enter your Twilio credentials.
+2. Go to 'Templates' to define your messages. Map a Message UID to a Twilio ContentSid and set the base variables.
+3. Go to 'Contacts' and add your contacts. Fill in any contact-specific variables needed by your templates.
+4. Come back here, enter the Message UID and your desired Messages Per Second (MPS) rate.
+5. Click the 'Send Messages' button to begin.</t>
         </is>
       </c>
     </row>
@@ -510,12 +495,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>GOLD_HINDI_01</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>&lt;- Enter the Message UID of the template you want to send.</t>
+          <t>PROMO_01</t>
         </is>
       </c>
     </row>
@@ -528,29 +508,12 @@
       <c r="C6" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>&lt;- Set your desired sending rate (e.g., 1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>The 'Send Messages' button will be located in this area. You will need to add it manually after the macro is embedded. See User Guide for instructions.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A8:D8"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -562,29 +525,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:S3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -609,84 +551,84 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{1}}</t>
+          <t>Contact Variable {{1}}</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{2}}</t>
+          <t>Contact Variable {{2}}</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{3}}</t>
+          <t>Contact Variable {{3}}</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{4}}</t>
+          <t>Contact Variable {{4}}</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{5}}</t>
+          <t>Contact Variable {{5}}</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{6}}</t>
+          <t>Contact Variable {{6}}</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{7}}</t>
+          <t>Contact Variable {{7}}</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{8}}</t>
+          <t>Contact Variable {{8}}</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{9}}</t>
+          <t>Contact Variable {{9}}</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{10}}</t>
+          <t>Contact Variable {{10}}</t>
         </is>
       </c>
       <c r="O1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{11}}</t>
+          <t>Contact Variable {{11}}</t>
         </is>
       </c>
       <c r="P1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{12}}</t>
+          <t>Contact Variable {{12}}</t>
         </is>
       </c>
       <c r="Q1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{13}}</t>
+          <t>Contact Variable {{13}}</t>
         </is>
       </c>
       <c r="R1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{14}}</t>
+          <t>Contact Variable {{14}}</t>
         </is>
       </c>
       <c r="S1" s="2" t="inlineStr">
         <is>
-          <t>Variable {{15}}</t>
+          <t>Contact Variable {{15}}</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Test Contact 1</t>
+          <t>Manish Jain</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -702,24 +644,44 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Value1A</t>
+          <t>Brake Mould Design</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Value2A</t>
+          <t>95000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Value3A</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14 Sept 2025</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>18 Sept 2025</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>KK Enterprises</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Plot 123, Industrial Area, Delhi</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>KK_enter.png</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -731,7 +693,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Test Contact 2</t>
+          <t>Priya Singh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -741,26 +703,50 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Value1B</t>
+          <t>Engine Block Design</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Value2B</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>125000</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>15 Sept 2025</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20 Sept 2025</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>PS Innovations</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>456 Tech Park, Bangalore</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PS_inno.png</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -769,61 +755,7 @@
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Test Contact 3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>447123456789</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Value1C</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Value2C</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Value3C</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Value4C</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-    </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Yes,No"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -834,13 +766,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
@@ -850,55 +777,147 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Template Content</t>
+          <t>ContentSid</t>
         </is>
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="200" customHeight="1">
+          <t>Base Variable {{1}}</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{2}}</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{3}}</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{4}}</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{5}}</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{6}}</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{7}}</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{8}}</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{9}}</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{10}}</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{11}}</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{12}}</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{13}}</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{14}}</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>Base Variable {{15}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GOLD_HINDI_01</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>नमस्ते! 🙏
-आज का सोने का भाव:
-22k: {{1}}
-20k: {{2}}
-{{3}}
-{{4}}
-सराफा बाज़ार, मेरठ शहर
-शुभ दिन! ✨</t>
+          <t>PROMO_01</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>HXed1028a89b9e341576ac8dd83207d268</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gold Price Template (Hindi)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GREETING_ENG_01</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>Hello {{1}}! This is a test message from the Twilio Excel Sender.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Simple English Greeting</t>
-        </is>
-      </c>
+          <t>{{contact_var_1}}</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>{{contact_var_2}}</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>{{contact_var_3}}</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>{{contact_var_4}}</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{{contact_var_5}}</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>{{contact_var_6}}</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>{{contact_var_7}}</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>{{contact_var_8}}</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>{{contact_var_9}}</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -911,63 +930,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Timestamp</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Twilio Account SID</t>
-        </is>
-      </c>
-      <c r="B2" s="10" t="inlineStr">
-        <is>
-          <t>Enter your ACxxxxxxxx SID here</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Twilio Auth Token</t>
-        </is>
-      </c>
-      <c r="B3" s="10" t="inlineStr">
-        <is>
-          <t>Enter your Auth Token here</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Twilio 'From' Number</t>
-        </is>
-      </c>
-      <c r="B4" s="10" t="inlineStr">
-        <is>
-          <t>Enter your Twilio WhatsApp number here (e.g. +14155238886)</t>
+          <t>Contact Name</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Contact Number</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Message UID</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Twilio Response</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="DC11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -978,46 +976,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Timestamp</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>Contact Name</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Contact Number</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Message UID</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>Twilio Response</t>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Twilio Account SID</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Enter your ACxxxxxxxx SID here</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Twilio Auth Token</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Enter your Auth Token here</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Twilio 'From' Number</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Enter your Twilio WhatsApp number here (e.g. +14155238886)</t>
         </is>
       </c>
     </row>

--- a/TwilioSender.xlsx
+++ b/TwilioSender.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +33,10 @@
       <b val="1"/>
       <color rgb="004F81BD"/>
       <sz val="18"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00595959"/>
     </font>
     <font>
       <b val="1"/>
@@ -77,14 +81,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -468,16 +475,21 @@
           <t>Twilio WhatsApp Messenger</t>
         </is>
       </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Version 2.0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>How to Use</t>
         </is>
       </c>
     </row>
     <row r="4" ht="100" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>1. Go to 'Settings' to enter your Twilio credentials.
 2. Go to 'Templates' to define your messages. Map a Message UID to a Twilio ContentSid and set the base variables.
@@ -488,30 +500,30 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Active Message UID:</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>PROMO_01</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Messages Per Second (MPS):</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A3:D3"/>
   </mergeCells>
@@ -529,97 +541,97 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>WhatsApp Number</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Send?</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{1}}</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{2}}</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{3}}</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{4}}</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{5}}</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{6}}</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{7}}</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{8}}</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{9}}</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{10}}</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{11}}</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{12}}</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{13}}</t>
         </is>
       </c>
-      <c r="R1" s="2" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{14}}</t>
         </is>
       </c>
-      <c r="S1" s="2" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Contact Variable {{15}}</t>
         </is>
@@ -770,87 +782,87 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Message UID</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ContentSid</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{1}}</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{2}}</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{3}}</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{4}}</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{5}}</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{6}}</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{7}}</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{8}}</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{9}}</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{10}}</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{11}}</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{12}}</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{13}}</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{14}}</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{15}}</t>
         </is>
@@ -934,32 +946,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Timestamp</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Contact Number</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Message UID</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Twilio Response</t>
         </is>
@@ -980,12 +992,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Value</t>
         </is>

--- a/TwilioSender.xlsx
+++ b/TwilioSender.xlsx
@@ -778,7 +778,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -794,75 +794,90 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Template Content (Reference Only)</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Sample Final Content (Preview)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
           <t>Base Variable {{1}}</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{2}}</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{3}}</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{4}}</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{5}}</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{6}}</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="L1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{7}}</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="M1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{8}}</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="N1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{9}}</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="O1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{10}}</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="P1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{11}}</t>
         </is>
       </c>
-      <c r="N1" s="3" t="inlineStr">
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{12}}</t>
         </is>
       </c>
-      <c r="O1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{13}}</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{14}}</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="T1" s="3" t="inlineStr">
         <is>
           <t>Base Variable {{15}}</t>
         </is>
@@ -881,55 +896,78 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>Promotional offer for unutilized production capacity.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Special Offer: {{1}}
+Regular Price: ₹{{2}} | Your Discount: {{3}}%
+Offer valid from {{4}} to {{5}}.
+Visit us or connect today.
+{{6}}
+{{7}}
+(Attached: {{8}})</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Special Offer: {{contact_var_1}}
+Regular Price: ₹{{contact_var_2}} | Your Discount: {{contact_var_3}}%
+Offer valid from {{contact_var_4}} to {{contact_var_5}}.
+Visit us or connect today.
+{{contact_var_6}}
+{{contact_var_7}}
+(Attached: {{contact_var_8}})</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>{{contact_var_1}}</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>{{contact_var_2}}</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>{{contact_var_3}}</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>{{contact_var_4}}</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>{{contact_var_5}}</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>{{contact_var_6}}</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>{{contact_var_7}}</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>{{contact_var_8}}</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>{{contact_var_9}}</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
